--- a/data/desempeno/kpi_desempeno_2026-03-02.xlsx
+++ b/data/desempeno/kpi_desempeno_2026-03-02.xlsx
@@ -1143,7 +1143,7 @@
     <row r="31">
       <c t="inlineStr" r="A31" s="0">
         <is>
-          <t xml:space="preserve">Reporte generado: 09-03-2026 07:03 a. m. </t>
+          <t xml:space="preserve">Reporte generado: 11-03-2026 08:29 a. m. </t>
         </is>
       </c>
     </row>
